--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4344.74</v>
+        <v>4297.47</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>52860.96</v>
+        <v>53120.63</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15219.05</v>
+        <v>15269.54</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1660.42</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>193131.89</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10182.93</v>
+        <v>10018.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -877,6 +877,128 @@
         <v>10018.6</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>511077-95-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>5049.19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1078634-13-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.402.010-5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43733.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -999,6 +999,67 @@
         <v>43733.05</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>299-168-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>77200.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-rios.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
